--- a/artfynd/A 36371-2022 artfynd.xlsx
+++ b/artfynd/A 36371-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36371-2022 artfynd.xlsx
+++ b/artfynd/A 36371-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96790153</v>
+        <v>111574338</v>
       </c>
       <c r="B2" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tivsjöflon, S om, Jmt</t>
+          <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563180.4398927827</v>
+        <v>562558</v>
       </c>
       <c r="R2" t="n">
-        <v>6954830.089217463</v>
+        <v>6954757</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +741,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,86 +767,65 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>100-årig barrblandskog</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>1 substratenheter # brandhögstubbe</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96790162</v>
+        <v>111574403</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tivsjöflon, SV om, Jmt</t>
+          <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562818.3797001784</v>
+        <v>562547</v>
       </c>
       <c r="R3" t="n">
-        <v>6954828.675370974</v>
+        <v>6954768</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,22 +849,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,78 +875,65 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>äldre lågörtsgranskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96790154</v>
+        <v>111575796</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tivsjöflon, S om, Jmt</t>
+          <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563210.1236460152</v>
+        <v>562855</v>
       </c>
       <c r="R4" t="n">
-        <v>6954767.794879766</v>
+        <v>6954651</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,22 +957,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,40 +983,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>120-årig tall- och lärkskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96790156</v>
+        <v>111576037</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1062,37 +1010,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tivsjöflon, S om, Jmt</t>
+          <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563218.6638480126</v>
+        <v>562853</v>
       </c>
       <c r="R5" t="n">
-        <v>6954633.968339853</v>
+        <v>6954606</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1116,22 +1065,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,48 +1091,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>120-årig, bördig tallskog med lärkinslag</t>
-        </is>
-      </c>
-      <c r="AN5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>1 substratenheter # björkhögstubbe av äldre generation björk</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>96790161</v>
       </c>
       <c r="B6" t="n">
-        <v>90155</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562802.2642044</v>
+        <v>562802</v>
       </c>
       <c r="R6" t="n">
-        <v>6954854.522671128</v>
+        <v>6954855</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1248,19 +1175,9 @@
           <t>2021-08-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-08-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1304,53 +1221,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96790164</v>
+        <v>111574334</v>
       </c>
       <c r="B7" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tivsjöflon, SV om, Jmt</t>
+          <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562815.4646543558</v>
+        <v>562558</v>
       </c>
       <c r="R7" t="n">
-        <v>6954740.519283876</v>
+        <v>6954757</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1374,22 +1287,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1400,86 +1313,65 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>äldre lågörtsgranskog</t>
-        </is>
-      </c>
-      <c r="AN7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grov asp</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96790160</v>
+        <v>111574429</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tivsjöflon, SV om, Jmt</t>
+          <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562764.6392202278</v>
+        <v>562547</v>
       </c>
       <c r="R8" t="n">
-        <v>6954875.83058611</v>
+        <v>6954768</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1503,22 +1395,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1529,75 +1421,61 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>äldre lågörtsgranskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96790158</v>
+        <v>96790164</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tivsjöflon, S om, Jmt</t>
+          <t>Tivsjöflon, SV om, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562950.8418263097</v>
+        <v>562816</v>
       </c>
       <c r="R9" t="n">
-        <v>6954870.204641113</v>
+        <v>6954741</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1627,21 +1505,11 @@
           <t>2021-08-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-08-09</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1654,6 +1522,14 @@
       <c r="AI9" t="inlineStr">
         <is>
           <t>äldre lågörtsgranskog</t>
+        </is>
+      </c>
+      <c r="AN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov asp</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1675,53 +1551,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96790159</v>
+        <v>111575785</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tivsjöflon, SV om, Jmt</t>
+          <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562863.0840317797</v>
+        <v>562859</v>
       </c>
       <c r="R10" t="n">
-        <v>6954918.084710945</v>
+        <v>6954661</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1745,22 +1617,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1771,78 +1643,65 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>äldre lågörtsgranskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96790163</v>
+        <v>111576401</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tivsjöflon, SV om, Jmt</t>
+          <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562815.9860415705</v>
+        <v>562964</v>
       </c>
       <c r="R11" t="n">
-        <v>6954785.497493515</v>
+        <v>6954711</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1866,22 +1725,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1892,62 +1751,48 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>äldre lågörtsgranskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96790157</v>
+        <v>96790153</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1957,10 +1802,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562916.7652821741</v>
+        <v>563180</v>
       </c>
       <c r="R12" t="n">
-        <v>6954777.783577246</v>
+        <v>6954830</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1990,21 +1835,11 @@
           <t>2021-08-09</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-08-09</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2016,7 +1851,15 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>äldre lågörtsgranskog</t>
+          <t>100-årig barrblandskog</t>
+        </is>
+      </c>
+      <c r="AN12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>1 substratenheter # brandhögstubbe</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2038,15 +1881,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111574338</v>
+        <v>96790156</v>
       </c>
       <c r="B13" t="n">
-        <v>89686</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2054,38 +1892,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tivsjöflon, Jmt</t>
+          <t>Tivsjöflon, S om, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562557.3535548041</v>
+        <v>563218</v>
       </c>
       <c r="R13" t="n">
-        <v>6954757.635990249</v>
+        <v>6954634</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2109,22 +1946,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:26</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:26</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2135,31 +1962,43 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>120-årig, bördig tallskog med lärkinslag</t>
+        </is>
+      </c>
+      <c r="AN13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>1 substratenheter # björkhögstubbe av äldre generation björk</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111574334</v>
+        <v>129982476</v>
       </c>
       <c r="B14" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2167,38 +2006,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562557.3535548041</v>
+        <v>562483</v>
       </c>
       <c r="R14" t="n">
-        <v>6954757.635990249</v>
+        <v>6954658</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2222,22 +2065,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:26</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:26</t>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2252,66 +2090,65 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111576401</v>
+        <v>129986595</v>
       </c>
       <c r="B15" t="n">
-        <v>89369</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562964.914807545</v>
+        <v>562713</v>
       </c>
       <c r="R15" t="n">
-        <v>6954710.791209211</v>
+        <v>6954614</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2335,22 +2172,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>16:51</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>16:51</t>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2365,52 +2197,51 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111575785</v>
+        <v>111574240</v>
       </c>
       <c r="B16" t="n">
-        <v>89845</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2418,10 +2249,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562859.2727272335</v>
+        <v>562533</v>
       </c>
       <c r="R16" t="n">
-        <v>6954660.134623887</v>
+        <v>6954848</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2453,7 +2284,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2463,7 +2294,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Familj med 5 talltitor. Permanent revir</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2490,15 +2326,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111575796</v>
+        <v>111578127</v>
       </c>
       <c r="B17" t="n">
-        <v>89686</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2506,35 +2337,40 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562855.7640570825</v>
+        <v>562938</v>
       </c>
       <c r="R17" t="n">
-        <v>6954651.349091855</v>
+        <v>6954541</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2566,7 +2402,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2576,7 +2412,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2603,15 +2439,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111573569</v>
+        <v>96790154</v>
       </c>
       <c r="B18" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2637,20 +2468,19 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tivsjöflon, Jmt</t>
+          <t>Tivsjöflon, S om, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562701.9737813871</v>
+        <v>563210</v>
       </c>
       <c r="R18" t="n">
-        <v>6954788.374143652</v>
+        <v>6954768</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2674,22 +2504,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2700,31 +2520,35 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>120-årig tall- och lärkskog</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>111574030</v>
+        <v>96790157</v>
       </c>
       <c r="B19" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2750,20 +2574,19 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tivsjöflon, Jmt</t>
+          <t>Tivsjöflon, S om, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562576.2301468613</v>
+        <v>562917</v>
       </c>
       <c r="R19" t="n">
-        <v>6954852.517936011</v>
+        <v>6954778</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2787,27 +2610,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>15:23</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2818,74 +2626,73 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>äldre lågörtsgranskog</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>111574240</v>
+        <v>96790158</v>
       </c>
       <c r="B20" t="n">
-        <v>56543</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tivsjöflon, Jmt</t>
+          <t>Tivsjöflon, S om, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562533.1227179464</v>
+        <v>562951</v>
       </c>
       <c r="R20" t="n">
-        <v>6954848.029061474</v>
+        <v>6954870</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2909,27 +2716,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>15:26</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Familj med 5 talltitor. Permanent revir</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2940,31 +2732,35 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>äldre lågörtsgranskog</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>111574128</v>
+        <v>96790159</v>
       </c>
       <c r="B21" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2990,20 +2786,19 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Tivsjöflon, Jmt</t>
+          <t>Tivsjöflon, SV om, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562555.4143375416</v>
+        <v>562863</v>
       </c>
       <c r="R21" t="n">
-        <v>6954835.60431945</v>
+        <v>6954918</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3027,22 +2822,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>15:26</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>15:26</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3053,75 +2838,73 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>äldre lågörtsgranskog</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111578127</v>
+        <v>96790160</v>
       </c>
       <c r="B22" t="n">
-        <v>56543</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tivsjöflon, Jmt</t>
+          <t>Tivsjöflon, SV om, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562937.8205991766</v>
+        <v>562765</v>
       </c>
       <c r="R22" t="n">
-        <v>6954541.406048392</v>
+        <v>6954876</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3145,22 +2928,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>18:30</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>18:30</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3171,31 +2944,35 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>äldre lågörtsgranskog</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>111573803</v>
+        <v>96790162</v>
       </c>
       <c r="B23" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3221,20 +2998,19 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Tivsjöflon, Jmt</t>
+          <t>Tivsjöflon, SV om, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562591.0245237258</v>
+        <v>562819</v>
       </c>
       <c r="R23" t="n">
-        <v>6954847.751526525</v>
+        <v>6954829</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3258,22 +3034,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>15:14</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>15:14</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3284,31 +3050,35 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>äldre lågörtsgranskog</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>111576771</v>
+        <v>96790163</v>
       </c>
       <c r="B24" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3334,20 +3104,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Tivsjöflon, Jmt</t>
+          <t>Tivsjöflon, SV om, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562807.4867926922</v>
+        <v>562816</v>
       </c>
       <c r="R24" t="n">
-        <v>6954821.585021482</v>
+        <v>6954786</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3371,22 +3140,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>17:24</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>17:24</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3397,31 +3156,35 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>äldre lågörtsgranskog</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>111576450</v>
+        <v>111573533</v>
       </c>
       <c r="B25" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3454,10 +3217,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562979.5212303887</v>
+        <v>562702</v>
       </c>
       <c r="R25" t="n">
-        <v>6954739.97881452</v>
+        <v>6954788</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3487,24 +3250,9 @@
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>17:10</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>17:10</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3531,15 +3279,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>111573866</v>
+        <v>111573746</v>
       </c>
       <c r="B26" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3572,10 +3315,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562601.7570288588</v>
+        <v>562601</v>
       </c>
       <c r="R26" t="n">
-        <v>6954814.918206804</v>
+        <v>6954815</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3607,7 +3350,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3617,7 +3360,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3644,15 +3387,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>111578197</v>
+        <v>111573803</v>
       </c>
       <c r="B27" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3685,10 +3423,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>563026.0554397166</v>
+        <v>562591</v>
       </c>
       <c r="R27" t="n">
-        <v>6954541.256262898</v>
+        <v>6954848</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3720,7 +3458,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3730,7 +3468,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3757,15 +3495,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>111574689</v>
+        <v>111573948</v>
       </c>
       <c r="B28" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3798,10 +3531,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562517.0252856832</v>
+        <v>562576</v>
       </c>
       <c r="R28" t="n">
-        <v>6954776.14289257</v>
+        <v>6954853</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3833,7 +3566,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3843,7 +3576,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3870,15 +3603,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>111575868</v>
+        <v>111574128</v>
       </c>
       <c r="B29" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3911,10 +3639,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562854.9195222461</v>
+        <v>562555</v>
       </c>
       <c r="R29" t="n">
-        <v>6954623.341454657</v>
+        <v>6954836</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3946,7 +3674,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3956,7 +3684,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3986,12 +3714,7 @@
         <v>111574509</v>
       </c>
       <c r="B30" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4024,10 +3747,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562529.1073683554</v>
+        <v>562529</v>
       </c>
       <c r="R30" t="n">
-        <v>6954769.030357216</v>
+        <v>6954769</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4096,37 +3819,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>111574403</v>
+        <v>111574689</v>
       </c>
       <c r="B31" t="n">
-        <v>89686</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4137,10 +3855,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562547.0565141424</v>
+        <v>562517</v>
       </c>
       <c r="R31" t="n">
-        <v>6954767.535469687</v>
+        <v>6954776</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4172,7 +3890,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4182,7 +3900,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4209,37 +3927,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>111576037</v>
+        <v>111575868</v>
       </c>
       <c r="B32" t="n">
-        <v>89686</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4250,10 +3963,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562852.9463231879</v>
+        <v>562855</v>
       </c>
       <c r="R32" t="n">
-        <v>6954606.325244571</v>
+        <v>6954623</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4285,7 +3998,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4295,7 +4008,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4322,37 +4035,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>111574429</v>
+        <v>111576450</v>
       </c>
       <c r="B33" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4363,10 +4071,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562547.0565141424</v>
+        <v>562979</v>
       </c>
       <c r="R33" t="n">
-        <v>6954767.535469687</v>
+        <v>6954740</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4398,7 +4106,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4408,7 +4116,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4432,6 +4145,212 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>111576771</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Tivsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>562808</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6954821</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2023-08-19</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2023-08-19</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>111578197</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Tivsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>563026</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6954541</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2023-08-19</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2023-08-19</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36371-2022 artfynd.xlsx
+++ b/artfynd/A 36371-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111574338</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111574403</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111575796</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111576037</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1218,6 +1243,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790161</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1326,6 +1356,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111574334</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1434,6 +1469,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111574429</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1548,6 +1588,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790164</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1656,6 +1701,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111575785</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1764,6 +1814,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111576401</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1878,6 +1933,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790153</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1992,6 +2052,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790156</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2099,6 +2164,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129982476</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2206,6 +2276,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129986595</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2323,6 +2398,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111574240</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2436,6 +2516,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111578127</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2542,6 +2627,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790154</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2648,6 +2738,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790157</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2754,6 +2849,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790158</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2860,6 +2960,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790159</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2966,6 +3071,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790160</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3072,6 +3182,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790162</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3178,6 +3293,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790163</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3276,6 +3396,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111573533</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3384,6 +3509,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111573746</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3492,6 +3622,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111573803</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3600,6 +3735,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111573948</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3708,6 +3848,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111574128</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3816,6 +3961,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111574509</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3924,6 +4074,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111574689</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4032,6 +4187,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111575868</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4145,6 +4305,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111576450</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4253,6 +4418,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111576771</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4351,8 +4521,49 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111578197</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>